--- a/research/traditional_assets/database/data/barbados/barbados_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/barbados/barbados_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00104</v>
+        <v>0.0266</v>
       </c>
       <c r="E2">
-        <v>-0.0275</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.007651582156389571</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.006740499498440022</v>
       </c>
       <c r="K2">
-        <v>121.8</v>
+        <v>173</v>
       </c>
       <c r="L2">
-        <v>0.234727307766429</v>
+        <v>0.2883333333333333</v>
       </c>
       <c r="M2">
-        <v>31.542</v>
+        <v>63.1</v>
       </c>
       <c r="N2">
-        <v>0.02213629026598357</v>
+        <v>0.04979875305816431</v>
       </c>
       <c r="O2">
-        <v>0.2589655172413793</v>
+        <v>0.3647398843930636</v>
       </c>
       <c r="P2">
-        <v>31.542</v>
+        <v>63.1</v>
       </c>
       <c r="Q2">
-        <v>0.02213629026598357</v>
+        <v>0.04979875305816431</v>
       </c>
       <c r="R2">
-        <v>0.2589655172413793</v>
+        <v>0.3647398843930636</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2633.4</v>
+        <v>2343.9</v>
       </c>
       <c r="V2">
-        <v>1.848129693311811</v>
+        <v>1.849814537132034</v>
       </c>
       <c r="W2">
-        <v>0.111784140969163</v>
+        <v>0.1542164378677126</v>
       </c>
       <c r="X2">
-        <v>0.08372640899079326</v>
+        <v>0.1278309950181759</v>
       </c>
       <c r="Y2">
-        <v>0.02805773197836975</v>
-      </c>
-      <c r="Z2">
-        <v>-0.588522173074742</v>
-      </c>
-      <c r="AA2">
-        <v>-0</v>
+        <v>0.02638544284953673</v>
       </c>
       <c r="AB2">
-        <v>0.08383219434542599</v>
-      </c>
-      <c r="AC2">
-        <v>-0.08383219434542599</v>
+        <v>0.1280611183338526</v>
       </c>
       <c r="AD2">
-        <v>26.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>20.69525353083129</v>
       </c>
       <c r="AF2">
-        <v>26.2</v>
+        <v>87.29525353083129</v>
       </c>
       <c r="AG2">
-        <v>-2607.2</v>
+        <v>-2256.604746469169</v>
       </c>
       <c r="AH2">
-        <v>0.01805526841706291</v>
+        <v>0.06445330733643487</v>
       </c>
       <c r="AI2">
-        <v>0.02355903246110961</v>
+        <v>0.07003817872664253</v>
       </c>
       <c r="AJ2">
-        <v>2.20519326736023</v>
+        <v>2.280539587628426</v>
       </c>
       <c r="AK2">
-        <v>1.713797410109775</v>
+        <v>2.056122995120515</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>7.628865979381442</v>
+      </c>
+      <c r="AP2">
+        <v>-258.4885162049449</v>
       </c>
     </row>
     <row r="3">
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00104</v>
+        <v>0.0266</v>
       </c>
       <c r="E3">
-        <v>-0.0275</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,34 +719,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.007651582156389571</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.006740499498440022</v>
       </c>
       <c r="K3">
-        <v>121.8</v>
+        <v>173</v>
       </c>
       <c r="L3">
-        <v>0.234727307766429</v>
+        <v>0.2883333333333333</v>
       </c>
       <c r="M3">
-        <v>31.542</v>
+        <v>63.1</v>
       </c>
       <c r="N3">
-        <v>0.02213629026598357</v>
+        <v>0.04979875305816431</v>
       </c>
       <c r="O3">
-        <v>0.2589655172413793</v>
+        <v>0.3647398843930636</v>
       </c>
       <c r="P3">
-        <v>31.542</v>
+        <v>63.1</v>
       </c>
       <c r="Q3">
-        <v>0.02213629026598357</v>
+        <v>0.04979875305816431</v>
       </c>
       <c r="R3">
-        <v>0.2589655172413793</v>
+        <v>0.3647398843930636</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,61 +755,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2633.4</v>
+        <v>2343.9</v>
       </c>
       <c r="V3">
-        <v>1.848129693311811</v>
+        <v>1.849814537132034</v>
       </c>
       <c r="W3">
-        <v>0.111784140969163</v>
+        <v>0.1542164378677126</v>
       </c>
       <c r="X3">
-        <v>0.08372640899079326</v>
+        <v>0.1278309950181759</v>
       </c>
       <c r="Y3">
-        <v>0.02805773197836975</v>
-      </c>
-      <c r="Z3">
-        <v>-0.588522173074742</v>
-      </c>
-      <c r="AA3">
-        <v>-0</v>
+        <v>0.02638544284953673</v>
       </c>
       <c r="AB3">
-        <v>0.08383219434542599</v>
-      </c>
-      <c r="AC3">
-        <v>-0.08383219434542599</v>
+        <v>0.1280611183338526</v>
       </c>
       <c r="AD3">
-        <v>26.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>20.69525353083129</v>
       </c>
       <c r="AF3">
-        <v>26.2</v>
+        <v>87.29525353083129</v>
       </c>
       <c r="AG3">
-        <v>-2607.2</v>
+        <v>-2256.604746469169</v>
       </c>
       <c r="AH3">
-        <v>0.01805526841706291</v>
+        <v>0.06445330733643487</v>
       </c>
       <c r="AI3">
-        <v>0.02355903246110961</v>
+        <v>0.07003817872664253</v>
       </c>
       <c r="AJ3">
-        <v>2.20519326736023</v>
+        <v>2.280539587628426</v>
       </c>
       <c r="AK3">
-        <v>1.713797410109775</v>
+        <v>2.056122995120515</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>7.628865979381442</v>
+      </c>
+      <c r="AP3">
+        <v>-258.4885162049449</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/barbados/barbados_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/barbados/barbados_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0266</v>
+        <v>0.0794</v>
       </c>
       <c r="E2">
-        <v>0.04650000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007651582156389571</v>
+        <v>0.006547508517885987</v>
       </c>
       <c r="J2">
-        <v>0.006740499498440022</v>
+        <v>0.005892305802155506</v>
       </c>
       <c r="K2">
-        <v>173</v>
+        <v>264.1</v>
       </c>
       <c r="L2">
-        <v>0.2883333333333333</v>
+        <v>0.3760501210308985</v>
       </c>
       <c r="M2">
-        <v>63.1</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="N2">
-        <v>0.04979875305816431</v>
+        <v>0.04565959522067788</v>
       </c>
       <c r="O2">
-        <v>0.3647398843930636</v>
+        <v>0.2836046951912155</v>
       </c>
       <c r="P2">
-        <v>63.1</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.04979875305816431</v>
+        <v>0.04565959522067788</v>
       </c>
       <c r="R2">
-        <v>0.3647398843930636</v>
+        <v>0.2836046951912155</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,46 +636,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2343.9</v>
+        <v>1880.4</v>
       </c>
       <c r="V2">
-        <v>1.849814537132034</v>
+        <v>1.146305779078274</v>
       </c>
       <c r="W2">
-        <v>0.1542164378677126</v>
+        <v>0.2337374988937074</v>
       </c>
       <c r="X2">
-        <v>0.1278309950181759</v>
+        <v>0.09703480528981723</v>
       </c>
       <c r="Y2">
-        <v>0.02638544284953673</v>
+        <v>0.1367026936038902</v>
       </c>
       <c r="AB2">
-        <v>0.1280611183338526</v>
+        <v>0.09764589790103939</v>
       </c>
       <c r="AD2">
-        <v>66.59999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="AE2">
-        <v>20.69525353083129</v>
+        <v>21.00842383944336</v>
       </c>
       <c r="AF2">
-        <v>87.29525353083129</v>
+        <v>84.70842383944336</v>
       </c>
       <c r="AG2">
-        <v>-2256.604746469169</v>
+        <v>-1795.691576160557</v>
       </c>
       <c r="AH2">
-        <v>0.06445330733643487</v>
+        <v>0.04910324630547813</v>
       </c>
       <c r="AI2">
-        <v>0.07003817872664253</v>
+        <v>0.05893955423191041</v>
       </c>
       <c r="AJ2">
-        <v>2.280539587628426</v>
+        <v>11.56335469416566</v>
       </c>
       <c r="AK2">
-        <v>2.056122995120515</v>
+        <v>4.051727678844745</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>7.628865979381442</v>
+        <v>7.238636363636363</v>
       </c>
       <c r="AP2">
-        <v>-258.4885162049449</v>
+        <v>-204.055860927336</v>
       </c>
     </row>
     <row r="3">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0266</v>
+        <v>0.0794</v>
       </c>
       <c r="E3">
-        <v>0.04650000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -719,34 +719,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.007651582156389571</v>
+        <v>0.006547508517885987</v>
       </c>
       <c r="J3">
-        <v>0.006740499498440022</v>
+        <v>0.005892305802155506</v>
       </c>
       <c r="K3">
-        <v>173</v>
+        <v>264.1</v>
       </c>
       <c r="L3">
-        <v>0.2883333333333333</v>
+        <v>0.3760501210308985</v>
       </c>
       <c r="M3">
-        <v>63.1</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="N3">
-        <v>0.04979875305816431</v>
+        <v>0.04565959522067788</v>
       </c>
       <c r="O3">
-        <v>0.3647398843930636</v>
+        <v>0.2836046951912155</v>
       </c>
       <c r="P3">
-        <v>63.1</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.04979875305816431</v>
+        <v>0.04565959522067788</v>
       </c>
       <c r="R3">
-        <v>0.3647398843930636</v>
+        <v>0.2836046951912155</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,46 +755,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2343.9</v>
+        <v>1880.4</v>
       </c>
       <c r="V3">
-        <v>1.849814537132034</v>
+        <v>1.146305779078274</v>
       </c>
       <c r="W3">
-        <v>0.1542164378677126</v>
+        <v>0.2337374988937074</v>
       </c>
       <c r="X3">
-        <v>0.1278309950181759</v>
+        <v>0.09703480528981723</v>
       </c>
       <c r="Y3">
-        <v>0.02638544284953673</v>
+        <v>0.1367026936038902</v>
       </c>
       <c r="AB3">
-        <v>0.1280611183338526</v>
+        <v>0.09764589790103939</v>
       </c>
       <c r="AD3">
-        <v>66.59999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="AE3">
-        <v>20.69525353083129</v>
+        <v>21.00842383944336</v>
       </c>
       <c r="AF3">
-        <v>87.29525353083129</v>
+        <v>84.70842383944336</v>
       </c>
       <c r="AG3">
-        <v>-2256.604746469169</v>
+        <v>-1795.691576160557</v>
       </c>
       <c r="AH3">
-        <v>0.06445330733643487</v>
+        <v>0.04910324630547813</v>
       </c>
       <c r="AI3">
-        <v>0.07003817872664253</v>
+        <v>0.05893955423191041</v>
       </c>
       <c r="AJ3">
-        <v>2.280539587628426</v>
+        <v>11.56335469416566</v>
       </c>
       <c r="AK3">
-        <v>2.056122995120515</v>
+        <v>4.051727678844745</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>7.628865979381442</v>
+        <v>7.238636363636363</v>
       </c>
       <c r="AP3">
-        <v>-258.4885162049449</v>
+        <v>-204.055860927336</v>
       </c>
     </row>
   </sheetData>
